--- a/output/pdf_financials_xlsx/FUU.xlsx
+++ b/output/pdf_financials_xlsx/FUU.xlsx
@@ -2759,22 +2759,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.811448</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.333821</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>13.926224</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>19.257597</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>30.801355</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>36.2318</v>
       </c>
     </row>
     <row r="93">
@@ -4930,7 +4930,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -6074,7 +6078,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -6902,7 +6910,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -7606,7 +7618,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>5.811448</v>
       </c>

--- a/output/pdf_financials_xlsx/FUU.xlsx
+++ b/output/pdf_financials_xlsx/FUU.xlsx
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.026233</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.047359</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.423448</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1.788095</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>1.016425</v>
       </c>
     </row>
     <row r="13">
@@ -1100,22 +1100,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.612808</v>
+        <v>-4.639041</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.828642</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.670125</v>
+        <v>-5.717484</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-12.13566</v>
+        <v>-12.559108</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-15.326273</v>
+        <v>-17.114368</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-12.337909</v>
+        <v>-13.354334</v>
       </c>
     </row>
     <row r="28">
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.608045</v>
+        <v>-4.634278</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.825549</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.652334</v>
+        <v>-5.699693</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-12.108973</v>
+        <v>-12.532421</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-15.300485</v>
+        <v>-17.08858</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-12.310838</v>
+        <v>-13.327263</v>
       </c>
     </row>
     <row r="30">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.09667199999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.694948</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>12.6181</v>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.09667199999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.694948</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>14.915942</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.123527</v>
+        <v>0.026855</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.811962</v>
+        <v>0.117014</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.043227</v>
@@ -3547,16 +3547,16 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026199</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.039299</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.038696</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.041002</v>
       </c>
     </row>
     <row r="125">
@@ -3572,16 +3572,16 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026199</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.039299</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.038696</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.041002</v>
       </c>
     </row>
     <row r="126">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -9176,7 +9176,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -10346,7 +10350,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -11076,7 +11084,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -12958,7 +12970,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
@@ -15056,7 +15068,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">

--- a/output/pdf_financials_xlsx/FUU.xlsx
+++ b/output/pdf_financials_xlsx/FUU.xlsx
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.010326</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -11908,7 +11908,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E177" s="5" t="n">
         <v>0.010326</v>
       </c>

--- a/output/pdf_financials_xlsx/FUU.xlsx
+++ b/output/pdf_financials_xlsx/FUU.xlsx
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.073479</v>
+        <v>0.514482</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.119815</v>
+        <v>0.413463</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2677</v>
+        <v>1.256026</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.625947</v>
+        <v>2.440835</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.856938</v>
+        <v>3.918385</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.431591</v>
+        <v>3.341342</v>
       </c>
     </row>
     <row r="8">
@@ -664,7 +664,7 @@
         <v>20.029934</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.745877</v>
+        <v>3.655628</v>
       </c>
     </row>
     <row r="11">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.018301</v>
+        <v>-0.018301</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -2972,7 +2972,7 @@
         <v>-0.010371</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.373189</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.125181</v>
@@ -3097,7 +3097,7 @@
         <v>-0.09088</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.326895</v>
+        <v>-0.046294</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.733758</v>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>1.361197</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -3325,10 +3325,10 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.015127</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>-0.215553</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -7842,7 +7842,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -8578,7 +8582,11 @@
           <t>Proceeds from sale of plane investment</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -9454,7 +9462,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -9904,7 +9916,11 @@
           <t>Proceed from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -10812,7 +10828,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -12050,7 +12070,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E180" s="5" t="n">
         <v>-0.018301</v>
       </c>
@@ -12358,7 +12382,11 @@
           <t>Consulting and director fees 16</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -14578,7 +14606,11 @@
           <t>Consulting and director fees 15</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -16674,7 +16706,11 @@
           <t>Consulting and director fees 12</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -19550,7 +19586,11 @@
           <t>Consulting and director fees 9</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E345" s="5" t="n">
         <v>0.441003</v>
       </c>
@@ -20054,7 +20094,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E356" s="5" t="n">
         <v>0.018301</v>
       </c>
